--- a/internal_doc/05.测试设计/自动化/rest/sequoiadb引擎rest接口_hxn.xlsx
+++ b/internal_doc/05.测试设计/自动化/rest/sequoiadb引擎rest接口_hxn.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="243">
   <si>
     <t>命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1011,6 +1011,14 @@
   <si>
     <t>cmd：命令字
 name：表名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rest_basic_split_3.js</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1213,7 +1221,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1283,55 +1291,64 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1676,22 +1693,22 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="13.5">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G2" s="12" t="s">
@@ -1705,69 +1722,69 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="13.5">
-      <c r="A3" s="28"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="28"/>
+      <c r="A3" s="36"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="12" t="s">
         <v>81</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="29" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="13.5">
-      <c r="A4" s="28"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="28"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="36"/>
       <c r="G4" s="12" t="s">
         <v>83</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="35"/>
+      <c r="I4" s="30"/>
     </row>
     <row r="5" spans="1:9" ht="13.5">
-      <c r="A5" s="30"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="30"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="33"/>
       <c r="G5" s="14" t="s">
         <v>40</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="36"/>
+      <c r="I5" s="31"/>
     </row>
     <row r="6" spans="1:9" ht="13.5">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G6" s="12" t="s">
@@ -1781,12 +1798,12 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="13.5">
-      <c r="A7" s="30"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="30"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="33"/>
       <c r="G7" s="14" t="s">
         <v>40</v>
       </c>
@@ -1798,22 +1815,22 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G8" s="12" t="s">
@@ -1822,32 +1839,32 @@
       <c r="H8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="41" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="13.5">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="28"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
       <c r="G9" s="14" t="s">
         <v>76</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="38"/>
+      <c r="I9" s="42"/>
     </row>
     <row r="10" spans="1:9" ht="13.5">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="11"/>
-      <c r="F10" s="28"/>
+      <c r="F10" s="36"/>
       <c r="G10" s="14" t="s">
         <v>101</v>
       </c>
@@ -1859,12 +1876,12 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="13.5">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="30"/>
+      <c r="F11" s="33"/>
       <c r="G11" s="14" t="s">
         <v>45</v>
       </c>
@@ -1876,22 +1893,22 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="13.5">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G12" s="12" t="s">
@@ -1905,12 +1922,12 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="13.5">
-      <c r="A13" s="30"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="30"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="33"/>
       <c r="G13" s="14" t="s">
         <v>40</v>
       </c>
@@ -1922,22 +1939,22 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="13.5">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G14" s="14" t="s">
@@ -1951,54 +1968,54 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="13.5">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
       <c r="G15" s="15" t="s">
         <v>45</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="33" t="s">
+      <c r="I15" s="38" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="13.5">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
       <c r="G16" s="15" t="s">
         <v>44</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I16" s="33"/>
+      <c r="I16" s="38"/>
     </row>
     <row r="17" spans="1:9" ht="33" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G17" s="13" t="s">
@@ -2012,12 +2029,12 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="33" customHeight="1">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
       <c r="G18" s="13" t="s">
         <v>50</v>
       </c>
@@ -2029,12 +2046,12 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="33" customHeight="1">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
       <c r="E19" s="10"/>
-      <c r="F19" s="30"/>
+      <c r="F19" s="33"/>
       <c r="G19" s="13" t="s">
         <v>45</v>
       </c>
@@ -2046,22 +2063,22 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="35.1" customHeight="1">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="32" t="s">
         <v>90</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G20" s="13" t="s">
@@ -2075,12 +2092,12 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="35.1" customHeight="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
       <c r="E21" s="16"/>
-      <c r="F21" s="28"/>
+      <c r="F21" s="36"/>
       <c r="G21" s="13" t="s">
         <v>94</v>
       </c>
@@ -2092,54 +2109,54 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="35.1" customHeight="1">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
       <c r="E22" s="16"/>
-      <c r="F22" s="28"/>
+      <c r="F22" s="36"/>
       <c r="G22" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I22" s="34" t="s">
+      <c r="I22" s="29" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="35.1" customHeight="1">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
       <c r="E23" s="16"/>
-      <c r="F23" s="30"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="13" t="s">
         <v>56</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I23" s="36"/>
+      <c r="I23" s="31"/>
     </row>
     <row r="24" spans="1:9" ht="33" customHeight="1">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="F24" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G24" s="13" t="s">
@@ -2153,12 +2170,12 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="33" customHeight="1">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
       <c r="G25" s="13" t="s">
         <v>87</v>
       </c>
@@ -2170,12 +2187,12 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="33" customHeight="1">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="30"/>
+      <c r="F26" s="33"/>
       <c r="G26" s="13" t="s">
         <v>45</v>
       </c>
@@ -2187,52 +2204,52 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="13.5">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="32" t="s">
         <v>7</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="27" t="s">
+      <c r="F27" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>58</v>
       </c>
       <c r="H27" s="13"/>
-      <c r="I27" s="42" t="s">
+      <c r="I27" s="39" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="13.5">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
+      <c r="A28" s="36"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
       <c r="E28" s="16"/>
-      <c r="F28" s="28"/>
+      <c r="F28" s="36"/>
       <c r="G28" s="13" t="s">
         <v>60</v>
       </c>
       <c r="H28" s="13"/>
-      <c r="I28" s="43"/>
+      <c r="I28" s="40"/>
     </row>
     <row r="29" spans="1:9" ht="13.5">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
       <c r="E29" s="16"/>
-      <c r="F29" s="30"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="13" t="s">
         <v>45</v>
       </c>
@@ -2242,22 +2259,22 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="14.1" customHeight="1">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="32" t="s">
         <v>236</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G30" s="13" t="s">
@@ -2271,12 +2288,12 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="14.1" customHeight="1">
-      <c r="A31" s="28"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
+      <c r="A31" s="36"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
       <c r="G31" s="13" t="s">
         <v>61</v>
       </c>
@@ -2288,54 +2305,54 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="14.1" customHeight="1">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
+      <c r="A32" s="36"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
       <c r="G32" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I32" s="33" t="s">
+      <c r="I32" s="38" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="14.1" customHeight="1">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
       <c r="E33" s="10"/>
-      <c r="F33" s="30"/>
+      <c r="F33" s="33"/>
       <c r="G33" s="13" t="s">
         <v>56</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I33" s="33"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:9" ht="18" customHeight="1">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="32" t="s">
         <v>117</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G34" s="13" t="s">
@@ -2349,12 +2366,12 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
+      <c r="A35" s="36"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="28"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="13" t="s">
         <v>137</v>
       </c>
@@ -2366,54 +2383,54 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="18" customHeight="1">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
+      <c r="A36" s="36"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="28"/>
+      <c r="F36" s="36"/>
       <c r="G36" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I36" s="33" t="s">
+      <c r="I36" s="38" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="18" customHeight="1">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="30"/>
+      <c r="F37" s="33"/>
       <c r="G37" s="13" t="s">
         <v>56</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I37" s="33"/>
+      <c r="I37" s="38"/>
     </row>
     <row r="38" spans="1:9" ht="13.5">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="32" t="s">
         <v>122</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F38" s="27" t="s">
+      <c r="F38" s="32" t="s">
         <v>42</v>
       </c>
       <c r="G38" s="13" t="s">
@@ -2425,12 +2442,12 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="13.5">
-      <c r="A39" s="30"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="30"/>
+      <c r="F39" s="33"/>
       <c r="G39" s="13" t="s">
         <v>45</v>
       </c>
@@ -2442,22 +2459,22 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="13.5">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="32" t="s">
         <v>64</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F40" s="27" t="s">
+      <c r="F40" s="32" t="s">
         <v>145</v>
       </c>
       <c r="G40" s="13" t="s">
@@ -2471,54 +2488,54 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="13.5">
-      <c r="A41" s="28"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
+      <c r="A41" s="36"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
       <c r="E41" s="16"/>
-      <c r="F41" s="28"/>
+      <c r="F41" s="36"/>
       <c r="G41" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I41" s="33" t="s">
+      <c r="I41" s="38" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="13.5">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
       <c r="E42" s="16"/>
-      <c r="F42" s="30"/>
+      <c r="F42" s="33"/>
       <c r="G42" s="13" t="s">
         <v>67</v>
       </c>
       <c r="H42" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I42" s="33"/>
+      <c r="I42" s="38"/>
     </row>
     <row r="43" spans="1:9" ht="13.5">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="27" t="s">
+      <c r="C43" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="32" t="s">
         <v>112</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F43" s="27" t="s">
+      <c r="F43" s="32" t="s">
         <v>145</v>
       </c>
       <c r="G43" s="13" t="s">
@@ -2530,130 +2547,132 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="13.5">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
+      <c r="A44" s="36"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="28"/>
+      <c r="F44" s="36"/>
       <c r="G44" s="13" t="s">
         <v>104</v>
       </c>
       <c r="H44" s="13"/>
-      <c r="I44" s="23" t="s">
+      <c r="I44" s="28" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="27">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
+    <row r="45" spans="1:9" ht="13.5">
+      <c r="A45" s="36"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="36"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="20" t="s">
+      <c r="F45" s="36"/>
+      <c r="G45" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="I45" s="27" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="27">
+      <c r="A46" s="36"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="H45" s="13" t="s">
+      <c r="H46" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I45" s="18" t="s">
+      <c r="I46" s="18" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="13.5">
-      <c r="A46" s="28"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="13" t="s">
+    <row r="47" spans="1:9" ht="13.5">
+      <c r="A47" s="36"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="I46" s="34" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="13.5">
-      <c r="A47" s="28"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="13" t="s">
-        <v>106</v>
       </c>
       <c r="H47" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I47" s="35"/>
+      <c r="I47" s="29" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="48" spans="1:9" ht="13.5">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
+      <c r="A48" s="36"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="36"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="28"/>
+      <c r="F48" s="36"/>
       <c r="G48" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H48" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I48" s="35"/>
+      <c r="I48" s="30"/>
     </row>
     <row r="49" spans="1:9" ht="13.5">
-      <c r="A49" s="28"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
+      <c r="A49" s="36"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="36"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="28"/>
+      <c r="F49" s="36"/>
       <c r="G49" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H49" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I49" s="36"/>
+      <c r="I49" s="30"/>
     </row>
     <row r="50" spans="1:9" ht="13.5">
-      <c r="A50" s="28"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
+      <c r="A50" s="36"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="28"/>
+      <c r="F50" s="36"/>
       <c r="G50" s="13" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I50" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="I50" s="31"/>
     </row>
     <row r="51" spans="1:9" ht="13.5">
-      <c r="A51" s="30"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
+      <c r="A51" s="36"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="36"/>
+      <c r="D51" s="36"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="30"/>
+      <c r="F51" s="36"/>
       <c r="G51" s="13" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H51" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I51" s="36"/>
+      <c r="I51" s="46" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="52" spans="1:9" ht="24">
       <c r="A52" s="4" t="s">
@@ -2685,22 +2704,22 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A53" s="27" t="s">
+      <c r="A53" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="27" t="s">
+      <c r="C53" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="E53" s="27" t="s">
+      <c r="E53" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="F53" s="27" t="s">
+      <c r="F53" s="32" t="s">
         <v>146</v>
       </c>
       <c r="G53" s="13" t="s">
@@ -2712,12 +2731,12 @@
       <c r="I53" s="18"/>
     </row>
     <row r="54" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A54" s="28"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
+      <c r="A54" s="36"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
       <c r="G54" s="13" t="s">
         <v>155</v>
       </c>
@@ -2727,22 +2746,22 @@
       <c r="I54" s="18"/>
     </row>
     <row r="55" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="C55" s="27" t="s">
+      <c r="C55" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D55" s="27" t="s">
+      <c r="D55" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="E55" s="27" t="s">
+      <c r="E55" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="F55" s="27" t="s">
+      <c r="F55" s="32" t="s">
         <v>146</v>
       </c>
       <c r="G55" s="13" t="s">
@@ -2754,12 +2773,12 @@
       <c r="I55" s="18"/>
     </row>
     <row r="56" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A56" s="28"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
+      <c r="A56" s="36"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
       <c r="G56" s="13" t="s">
         <v>220</v>
       </c>
@@ -2769,22 +2788,22 @@
       <c r="I56" s="18"/>
     </row>
     <row r="57" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="C57" s="27" t="s">
+      <c r="C57" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D57" s="27" t="s">
+      <c r="D57" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="E57" s="27" t="s">
+      <c r="E57" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="F57" s="27" t="s">
+      <c r="F57" s="32" t="s">
         <v>146</v>
       </c>
       <c r="G57" s="13" t="s">
@@ -2796,12 +2815,12 @@
       <c r="I57" s="18"/>
     </row>
     <row r="58" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A58" s="28"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
+      <c r="A58" s="36"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
       <c r="G58" s="13" t="s">
         <v>223</v>
       </c>
@@ -2811,22 +2830,22 @@
       <c r="I58" s="18"/>
     </row>
     <row r="59" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="C59" s="27" t="s">
+      <c r="C59" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D59" s="27" t="s">
+      <c r="D59" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="27" t="s">
+      <c r="E59" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F59" s="27" t="s">
+      <c r="F59" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G59" s="13" t="s">
@@ -2838,12 +2857,12 @@
       <c r="I59" s="18"/>
     </row>
     <row r="60" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A60" s="28"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
+      <c r="A60" s="36"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
       <c r="G60" s="13" t="s">
         <v>225</v>
       </c>
@@ -2853,22 +2872,22 @@
       <c r="I60" s="18"/>
     </row>
     <row r="61" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="C61" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="E61" s="27" t="s">
+      <c r="E61" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F61" s="27" t="s">
+      <c r="F61" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G61" s="13" t="s">
@@ -2880,12 +2899,12 @@
       <c r="I61" s="18"/>
     </row>
     <row r="62" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A62" s="28"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
+      <c r="A62" s="36"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="36"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="36"/>
       <c r="G62" s="13" t="s">
         <v>218</v>
       </c>
@@ -2895,22 +2914,22 @@
       <c r="I62" s="18"/>
     </row>
     <row r="63" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="C63" s="27" t="s">
+      <c r="C63" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D63" s="27" t="s">
+      <c r="D63" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="E63" s="27" t="s">
+      <c r="E63" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F63" s="27" t="s">
+      <c r="F63" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G63" s="13" t="s">
@@ -2922,12 +2941,12 @@
       <c r="I63" s="18"/>
     </row>
     <row r="64" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A64" s="28"/>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
+      <c r="A64" s="36"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
       <c r="G64" s="13" t="s">
         <v>216</v>
       </c>
@@ -2937,22 +2956,22 @@
       <c r="I64" s="18"/>
     </row>
     <row r="65" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C65" s="27" t="s">
+      <c r="C65" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D65" s="27" t="s">
+      <c r="D65" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="E65" s="27" t="s">
+      <c r="E65" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F65" s="27" t="s">
+      <c r="F65" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G65" s="13" t="s">
@@ -2964,12 +2983,12 @@
       <c r="I65" s="18"/>
     </row>
     <row r="66" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A66" s="28"/>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
+      <c r="A66" s="36"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
       <c r="G66" s="13" t="s">
         <v>214</v>
       </c>
@@ -2979,22 +2998,22 @@
       <c r="I66" s="18"/>
     </row>
     <row r="67" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="B67" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="C67" s="27" t="s">
+      <c r="C67" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D67" s="27" t="s">
+      <c r="D67" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="E67" s="27" t="s">
+      <c r="E67" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="27" t="s">
+      <c r="F67" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G67" s="13" t="s">
@@ -3006,12 +3025,12 @@
       <c r="I67" s="18"/>
     </row>
     <row r="68" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A68" s="28"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
+      <c r="A68" s="36"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
       <c r="G68" s="13" t="s">
         <v>212</v>
       </c>
@@ -3021,22 +3040,22 @@
       <c r="I68" s="18"/>
     </row>
     <row r="69" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="C69" s="27" t="s">
+      <c r="C69" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E69" s="27" t="s">
+      <c r="E69" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F69" s="27" t="s">
+      <c r="F69" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G69" s="13" t="s">
@@ -3048,12 +3067,12 @@
       <c r="I69" s="18"/>
     </row>
     <row r="70" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A70" s="28"/>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
+      <c r="A70" s="36"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
       <c r="G70" s="13" t="s">
         <v>210</v>
       </c>
@@ -3063,22 +3082,22 @@
       <c r="I70" s="18"/>
     </row>
     <row r="71" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="C71" s="27" t="s">
+      <c r="C71" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D71" s="27" t="s">
+      <c r="D71" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="E71" s="27" t="s">
+      <c r="E71" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F71" s="27" t="s">
+      <c r="F71" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G71" s="13" t="s">
@@ -3090,12 +3109,12 @@
       <c r="I71" s="18"/>
     </row>
     <row r="72" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A72" s="28"/>
-      <c r="B72" s="28"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
+      <c r="A72" s="36"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
       <c r="G72" s="13" t="s">
         <v>208</v>
       </c>
@@ -3105,22 +3124,22 @@
       <c r="I72" s="18"/>
     </row>
     <row r="73" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A73" s="27" t="s">
+      <c r="A73" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="C73" s="27" t="s">
+      <c r="C73" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D73" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="E73" s="27" t="s">
+      <c r="E73" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F73" s="27" t="s">
+      <c r="F73" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G73" s="13" t="s">
@@ -3132,12 +3151,12 @@
       <c r="I73" s="18"/>
     </row>
     <row r="74" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A74" s="28"/>
-      <c r="B74" s="28"/>
-      <c r="C74" s="28"/>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="28"/>
+      <c r="A74" s="36"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
       <c r="G74" s="13" t="s">
         <v>205</v>
       </c>
@@ -3147,22 +3166,22 @@
       <c r="I74" s="18"/>
     </row>
     <row r="75" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A75" s="27" t="s">
+      <c r="A75" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="C75" s="27" t="s">
+      <c r="C75" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D75" s="27" t="s">
+      <c r="D75" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="E75" s="27" t="s">
+      <c r="E75" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F75" s="27" t="s">
+      <c r="F75" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="13" t="s">
@@ -3174,12 +3193,12 @@
       <c r="I75" s="18"/>
     </row>
     <row r="76" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A76" s="28"/>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="28"/>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
+      <c r="A76" s="36"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
       <c r="G76" s="13" t="s">
         <v>204</v>
       </c>
@@ -3189,22 +3208,22 @@
       <c r="I76" s="18"/>
     </row>
     <row r="77" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A77" s="27" t="s">
+      <c r="A77" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C77" s="27" t="s">
+      <c r="C77" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D77" s="27" t="s">
+      <c r="D77" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="E77" s="27" t="s">
+      <c r="E77" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F77" s="27" t="s">
+      <c r="F77" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G77" s="13" t="s">
@@ -3216,12 +3235,12 @@
       <c r="I77" s="18"/>
     </row>
     <row r="78" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A78" s="28"/>
-      <c r="B78" s="28"/>
-      <c r="C78" s="28"/>
-      <c r="D78" s="28"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="28"/>
+      <c r="A78" s="36"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
       <c r="G78" s="13" t="s">
         <v>202</v>
       </c>
@@ -3231,22 +3250,22 @@
       <c r="I78" s="18"/>
     </row>
     <row r="79" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A79" s="27" t="s">
+      <c r="A79" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="B79" s="27" t="s">
+      <c r="B79" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="C79" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D79" s="27" t="s">
+      <c r="D79" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E79" s="27" t="s">
+      <c r="E79" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F79" s="27" t="s">
+      <c r="F79" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G79" s="13" t="s">
@@ -3258,12 +3277,12 @@
       <c r="I79" s="18"/>
     </row>
     <row r="80" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A80" s="28"/>
-      <c r="B80" s="28"/>
-      <c r="C80" s="28"/>
-      <c r="D80" s="28"/>
-      <c r="E80" s="28"/>
-      <c r="F80" s="28"/>
+      <c r="A80" s="36"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
       <c r="G80" s="13" t="s">
         <v>200</v>
       </c>
@@ -3273,22 +3292,22 @@
       <c r="I80" s="18"/>
     </row>
     <row r="81" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A81" s="27" t="s">
+      <c r="A81" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C81" s="27" t="s">
+      <c r="C81" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D81" s="27" t="s">
+      <c r="D81" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="E81" s="27" t="s">
+      <c r="E81" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F81" s="27" t="s">
+      <c r="F81" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G81" s="13" t="s">
@@ -3300,12 +3319,12 @@
       <c r="I81" s="18"/>
     </row>
     <row r="82" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A82" s="28"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="28"/>
-      <c r="D82" s="28"/>
-      <c r="E82" s="28"/>
-      <c r="F82" s="28"/>
+      <c r="A82" s="36"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="36"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="36"/>
       <c r="G82" s="13" t="s">
         <v>198</v>
       </c>
@@ -3315,22 +3334,22 @@
       <c r="I82" s="18"/>
     </row>
     <row r="83" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A83" s="27" t="s">
+      <c r="A83" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C83" s="27" t="s">
+      <c r="C83" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D83" s="27" t="s">
+      <c r="D83" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="E83" s="27" t="s">
+      <c r="E83" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F83" s="27" t="s">
+      <c r="F83" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G83" s="13" t="s">
@@ -3342,12 +3361,12 @@
       <c r="I83" s="18"/>
     </row>
     <row r="84" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A84" s="28"/>
-      <c r="B84" s="28"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
+      <c r="A84" s="36"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
       <c r="G84" s="13" t="s">
         <v>196</v>
       </c>
@@ -3357,22 +3376,22 @@
       <c r="I84" s="18"/>
     </row>
     <row r="85" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A85" s="27" t="s">
+      <c r="A85" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="C85" s="27" t="s">
+      <c r="C85" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D85" s="27" t="s">
+      <c r="D85" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E85" s="27" t="s">
+      <c r="E85" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F85" s="27" t="s">
+      <c r="F85" s="32" t="s">
         <v>18</v>
       </c>
       <c r="G85" s="13" t="s">
@@ -3384,12 +3403,12 @@
       <c r="I85" s="18"/>
     </row>
     <row r="86" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A86" s="28"/>
-      <c r="B86" s="28"/>
-      <c r="C86" s="28"/>
-      <c r="D86" s="28"/>
-      <c r="E86" s="28"/>
-      <c r="F86" s="28"/>
+      <c r="A86" s="36"/>
+      <c r="B86" s="36"/>
+      <c r="C86" s="36"/>
+      <c r="D86" s="36"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="36"/>
       <c r="G86" s="13" t="s">
         <v>194</v>
       </c>
@@ -3399,22 +3418,22 @@
       <c r="I86" s="18"/>
     </row>
     <row r="87" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A87" s="29" t="s">
+      <c r="A87" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B87" s="29" t="s">
+      <c r="B87" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="C87" s="27" t="s">
+      <c r="C87" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D87" s="29" t="s">
+      <c r="D87" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="E87" s="29" t="s">
+      <c r="E87" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F87" s="29" t="s">
+      <c r="F87" s="45" t="s">
         <v>18</v>
       </c>
       <c r="G87" s="13" t="s">
@@ -3426,12 +3445,12 @@
       <c r="I87" s="18"/>
     </row>
     <row r="88" spans="1:9" ht="24.95" customHeight="1">
-      <c r="A88" s="29"/>
-      <c r="B88" s="29"/>
-      <c r="C88" s="28"/>
-      <c r="D88" s="29"/>
-      <c r="E88" s="29"/>
-      <c r="F88" s="29"/>
+      <c r="A88" s="45"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="45"/>
+      <c r="E88" s="45"/>
+      <c r="F88" s="45"/>
       <c r="G88" s="13" t="s">
         <v>192</v>
       </c>
@@ -3441,7 +3460,7 @@
       <c r="I88" s="18"/>
     </row>
     <row r="89" spans="1:9" ht="13.5">
-      <c r="F89" s="31" t="s">
+      <c r="F89" s="43" t="s">
         <v>147</v>
       </c>
       <c r="G89" s="26" t="s">
@@ -3455,7 +3474,7 @@
       </c>
     </row>
     <row r="90" spans="1:9" ht="13.5">
-      <c r="F90" s="32"/>
+      <c r="F90" s="44"/>
       <c r="G90" s="13" t="s">
         <v>39</v>
       </c>
@@ -3467,25 +3486,197 @@
       </c>
     </row>
     <row r="91" spans="1:9" ht="13.5">
-      <c r="F91" s="32"/>
+      <c r="F91" s="44"/>
       <c r="G91" s="13"/>
       <c r="H91" s="13"/>
       <c r="I91" s="18"/>
     </row>
     <row r="92" spans="1:9" ht="13.5">
-      <c r="F92" s="32"/>
+      <c r="F92" s="44"/>
       <c r="G92" s="13"/>
       <c r="H92" s="13"/>
       <c r="I92" s="18"/>
     </row>
     <row r="93" spans="1:9" ht="13.5">
-      <c r="F93" s="32"/>
+      <c r="F93" s="44"/>
       <c r="G93" s="13"/>
       <c r="H93" s="13"/>
       <c r="I93" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="197">
+  <mergeCells count="196">
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="F79:F80"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="F71:F72"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="F63:F64"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="A43:A51"/>
+    <mergeCell ref="B43:B51"/>
+    <mergeCell ref="C43:C51"/>
+    <mergeCell ref="D43:D51"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="F40:F42"/>
+    <mergeCell ref="F43:F51"/>
+    <mergeCell ref="F89:F93"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="F73:F74"/>
+    <mergeCell ref="F77:F78"/>
+    <mergeCell ref="F81:F82"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="F20:F23"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="I47:I50"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E12:E13"/>
@@ -3509,180 +3700,7 @@
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="E2:E5"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="I46:I49"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="A34:A37"/>
     <mergeCell ref="F8:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="F20:F23"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="F40:F42"/>
-    <mergeCell ref="F43:F51"/>
-    <mergeCell ref="F89:F93"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="A43:A51"/>
-    <mergeCell ref="B43:B51"/>
-    <mergeCell ref="C43:C51"/>
-    <mergeCell ref="D43:D51"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="F59:F60"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="F63:F64"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="F67:F68"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="F71:F72"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F77:F78"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="F79:F80"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="F81:F82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="F83:F84"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
